--- a/data/IKPA_AGUSTUS_2025.xlsx
+++ b/data/IKPA_AGUSTUS_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +544,11 @@
           <t>Satker</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -629,6 +634,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -714,6 +724,11 @@
           <t>PENGADILAN AGAMA MARTAPURA (401944)</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -799,6 +814,11 @@
           <t>PENGADILAN AGAMA MUARADUA (401945)</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -884,6 +904,11 @@
           <t>PENGADILAN AGAMA BATURAJA (402267)</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -969,6 +994,11 @@
           <t>PENGADILAN AGAMA BATURAJA (402268)</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1054,6 +1084,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440505)</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1139,6 +1174,11 @@
           <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1224,6 +1264,11 @@
           <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1309,6 +1354,11 @@
           <t>RUTAN KELAS II B BATURAJA (692339)</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1394,6 +1444,11 @@
           <t>POLRES OGAN KOMERING ULU SELATAN (665307)</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1479,6 +1534,11 @@
           <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN (667215)</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1564,6 +1624,11 @@
           <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1649,6 +1714,11 @@
           <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR (668529)</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1734,6 +1804,11 @@
           <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1819,6 +1894,11 @@
           <t>POLRES OGAN KOMERING ULU (641681)</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1904,6 +1984,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440506)</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1989,6 +2074,11 @@
           <t>PENGADILAN AGAMA MUARADUA (403410)</t>
         </is>
       </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2074,6 +2164,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440504)</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2159,6 +2254,11 @@
           <t>BAPAS KELAS II OKU INDUK (692625)</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2244,6 +2344,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418456)</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2329,6 +2434,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR (553099)</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2414,6 +2524,11 @@
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (111071)</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2499,6 +2614,11 @@
           <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2584,6 +2704,11 @@
           <t>PUSLATPUR KODIKLATAD (685001)</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2669,6 +2794,11 @@
           <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
         </is>
       </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2754,6 +2884,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR (597480)</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2839,6 +2974,11 @@
           <t>PENGADILAN NEGERI BATURAJA (098963)</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2924,6 +3064,11 @@
           <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN (670561)</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3009,6 +3154,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR (418471)</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3094,6 +3244,11 @@
           <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN (669055)</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3179,6 +3334,11 @@
           <t>POLRES OGAN KOMERING ULU TIMUR (665292)</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3264,6 +3424,11 @@
           <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN (656574)</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3349,6 +3514,11 @@
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666504)</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3434,6 +3604,11 @@
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666505)</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3519,6 +3694,11 @@
           <t>LAPAS KELAS II B MUARA DUA (692334)</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3604,6 +3784,11 @@
           <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR (656560)</t>
         </is>
       </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3689,6 +3874,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN (661192)</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3774,6 +3964,11 @@
           <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU (424245)</t>
         </is>
       </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3859,6 +4054,11 @@
           <t>LAPAS KELAS II B MARTAPURA (692340)</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3944,6 +4144,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440502)</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4029,6 +4234,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440503)</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4114,6 +4324,11 @@
           <t>KPU  KABUPATEN OGAN KOMERING ULU (656553)</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4199,6 +4414,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (418462)</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4284,6 +4504,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (424967)</t>
         </is>
       </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4369,6 +4594,11 @@
           <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4454,6 +4684,11 @@
           <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU (431142)</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4539,6 +4774,11 @@
           <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN (686503)</t>
         </is>
       </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4624,6 +4864,11 @@
           <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ (344894)</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4709,6 +4954,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418459)</t>
         </is>
       </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4794,6 +5044,11 @@
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
         </is>
       </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4879,6 +5134,11 @@
           <t>RUPBASAN KELAS II BATURAJA (692725)</t>
         </is>
       </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4964,6 +5224,11 @@
           <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (426066)</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5049,6 +5314,11 @@
           <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (662127)</t>
         </is>
       </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5134,6 +5404,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU (426050)</t>
         </is>
       </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5219,6 +5494,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418458)</t>
         </is>
       </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5304,6 +5584,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (553792)</t>
         </is>
       </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5389,6 +5674,11 @@
           <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR (111079)</t>
         </is>
       </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5474,6 +5764,11 @@
           <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (597558)</t>
         </is>
       </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5559,6 +5854,11 @@
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666501)</t>
         </is>
       </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5644,6 +5944,11 @@
           <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU (419006)</t>
         </is>
       </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5729,6 +6034,11 @@
           <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA (690801)</t>
         </is>
       </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5814,6 +6124,11 @@
           <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN (574370)</t>
         </is>
       </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5899,6 +6214,11 @@
           <t>PENGADILAN NEGERI BATURAJA (099228)</t>
         </is>
       </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5984,6 +6304,11 @@
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666502)</t>
         </is>
       </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6069,6 +6394,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418457)</t>
         </is>
       </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6154,6 +6484,11 @@
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666507)</t>
         </is>
       </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6239,6 +6574,11 @@
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418461)</t>
         </is>
       </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6322,6 +6662,11 @@
       <c r="W69" t="inlineStr">
         <is>
           <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR (691653)</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Upload</t>
         </is>
       </c>
     </row>

--- a/data/IKPA_AGUSTUS_2025.xlsx
+++ b/data/IKPA_AGUSTUS_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X69"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,10 +541,15 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Uraian Satker Final</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Satker</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -631,10 +636,15 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440507)</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -721,10 +731,15 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (401944)</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>PA MARTAPURA (401944)</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -811,10 +826,15 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>PA MUARADUA (401945)</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -901,10 +921,15 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>PA BATURAJA (402267)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -991,10 +1016,15 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>PA BATURAJA (402268)</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1081,10 +1111,15 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440505)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440505)</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1171,10 +1206,15 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
+        <is>
+          <t>PA MARTAPURA (403409)</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1261,10 +1301,15 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA (527975)</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1351,10 +1396,15 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
+        <is>
+          <t>RUTAN BATURAJA (692339)</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1441,10 +1491,15 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN (665307)</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
+        <is>
+          <t>POLRES OKUS (665307)</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1531,10 +1586,15 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN (667215)</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
+        <is>
+          <t>BPS OKUS (667215)</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1621,10 +1681,15 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
+        <is>
+          <t>KPP BATURAJA (410574)</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1711,10 +1776,15 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR (668529)</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
+        <is>
+          <t>BPS OKUT (668529)</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1801,10 +1871,15 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
+        <is>
+          <t>BPS OKU (428258)</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1891,10 +1966,15 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU (641681)</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
+        <is>
+          <t>POLRES OKU (641681)</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1981,10 +2061,15 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440506)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440506)</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2071,10 +2156,15 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (403410)</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
+        <is>
+          <t>PA  MUARADUA (403410)</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2161,10 +2251,15 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440504)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440504)</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2251,10 +2346,15 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK (692625)</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
+        <is>
+          <t>BAPAS OKU INDUK (692625)</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2341,10 +2441,15 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418456)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418456)</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2431,10 +2536,15 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR (553099)</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT (553099)</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2521,10 +2631,15 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (111071)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (111071)</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2546,7 +2661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>'007130</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2611,10 +2726,15 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
+        <is>
+          <t>KEJARI  OKU ('007130)</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2701,10 +2821,15 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD (685001)</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
+        <is>
+          <t>PUSLATPUR AD (685001)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2726,7 +2851,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2791,10 +2916,15 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
+        <is>
+          <t>KEJARI OKUT ('007190)</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2881,10 +3011,15 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR (597480)</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUT (597480)</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2906,7 +3041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2971,10 +3106,15 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (098963)</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
+        <is>
+          <t>PN BATURAJA ('098963)</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3061,10 +3201,15 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN (670561)</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
+        <is>
+          <t>BPN OKUS (670561)</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3151,10 +3296,15 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR (418471)</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUT (418471)</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3241,10 +3391,15 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN (669055)</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
+        <is>
+          <t>BPN OKUT (669055)</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3331,10 +3486,15 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR (665292)</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
+        <is>
+          <t>POLRES OKUT (665292)</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3421,10 +3581,15 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN (656574)</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
+        <is>
+          <t>KPU OKUS (656574)</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3511,10 +3676,15 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666504)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666504)</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3601,10 +3771,15 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666505)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666505)</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3691,10 +3866,15 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA (692334)</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
+        <is>
+          <t>LAPAS MUARA DUA (692334)</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3781,10 +3961,15 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR (656560)</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
+        <is>
+          <t>KPU OKUT (656560)</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3871,10 +4056,15 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN (661192)</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUS (661192)</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3961,10 +4151,15 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU (424245)</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU (424245)</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4051,10 +4246,15 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA (692340)</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
+        <is>
+          <t>LAPAS MARTAPURA (692340)</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4141,10 +4341,15 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440502)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440502)</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4231,10 +4436,15 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440503)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440503)</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4321,10 +4531,15 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU (656553)</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
+        <is>
+          <t>KPU OKU (656553)</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4411,10 +4626,15 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (418462)</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUS (418462)</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4501,10 +4721,15 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (424967)</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUT (424967)</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4526,7 +4751,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4591,10 +4816,15 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
+        <is>
+          <t>KEJARI  OKUS ('007208)</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4681,10 +4911,15 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU (431142)</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
+        <is>
+          <t>BPN OKU (431142)</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4771,10 +5006,15 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN (686503)</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
+        <is>
+          <t>BAWASLU OKUS (686503)</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4861,10 +5101,15 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ (344894)</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
+        <is>
+          <t>RUMKIT NOESMIR (344894)</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4951,10 +5196,15 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418459)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418459)</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5041,10 +5291,15 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666503)</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5131,10 +5386,15 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA (692725)</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
+        <is>
+          <t>RUPBASAN BATURAJA (692725)</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5221,10 +5481,15 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (426066)</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUT (426066)</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5311,10 +5576,15 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (662127)</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS (662127)</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5401,10 +5671,15 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU (426050)</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKU (426050)</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5491,10 +5766,15 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418458)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418458)</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5581,10 +5861,15 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (553792)</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUS (553792)</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5671,10 +5956,15 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR (111079)</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
+        <is>
+          <t>BNN OKUT (111079)</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5761,10 +6051,15 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (597558)</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
+        <is>
+          <t>MAN 2 OKUS (597558)</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5851,10 +6146,15 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666501)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666501)</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5941,10 +6241,15 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU (419006)</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
+        <is>
+          <t>BAWASLU OKU (419006)</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6031,10 +6336,15 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA (690801)</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
+        <is>
+          <t>LOKA LABKESMAS (690801)</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6121,10 +6431,15 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN (574370)</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUS (574370)</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6146,7 +6461,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6211,10 +6526,15 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (099228)</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
+        <is>
+          <t>PN BATURAJA ('099228)</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6301,10 +6621,15 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666502)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666502)</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6391,10 +6716,15 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418457)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418457)</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6481,10 +6811,15 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666507)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666507)</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6571,10 +6906,15 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418461)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418461)</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6661,10 +7001,15 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR (691653)</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
+        <is>
+          <t>DISNAKERTRANS OKUT (691653)</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
